--- a/PTBR/Lang/PTBR/Game/Floor.xlsx
+++ b/PTBR/Lang/PTBR/Game/Floor.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H132"/>
+  <dimension ref="A1:H139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col collapsed="1" width="16" customWidth="1" min="1" max="1"/>
@@ -3987,6 +3987,195 @@
         </is>
       </c>
     </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>EA 23.283</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>andar das nuvens</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>cloud floor</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>雲の床</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>EA 23.286</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>andar alienígena</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>alien floor</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>エイリアンの床</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>EA 23.288</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>andar do palco</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>stage floor</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>ステージの床</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>EA 23.289</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>andar do palco</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>stage floor</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>ステージの床</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>EA 23.289</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>andar alienígena</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>alien floor</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>エイリアンの床</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>EA 23.289</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>andar alienígena</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>alien floor</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>エイリアンの床</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>EA 23.289</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>andar alienígena</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>alien floor</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>エイリアンの床</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A2:H2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/PTBR/Lang/PTBR/Game/Floor.xlsx
+++ b/PTBR/Lang/PTBR/Game/Floor.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H139"/>
+  <dimension ref="A1:H132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col collapsed="1" width="16" customWidth="1" min="1" max="1"/>
@@ -3987,195 +3987,6 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>EA 23.283</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>andar das nuvens</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>cloud floor</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>雲の床</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>EA 23.286</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>andar alienígena</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>alien floor</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>エイリアンの床</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>EA 23.288</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>andar do palco</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>stage floor</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>ステージの床</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>EA 23.289</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>andar do palco</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>stage floor</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>ステージの床</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>EA 23.289</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>andar alienígena</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>alien floor</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>エイリアンの床</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>EA 23.289</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>andar alienígena</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>alien floor</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>エイリアンの床</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>EA 23.289</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>andar alienígena</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>alien floor</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>エイリアンの床</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <autoFilter ref="A2:H2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
